--- a/sampleprojects/CorporateTax/excel/states/WV_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/WV_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>DT: Determine WV Filing Requirement</t>
   </si>
@@ -148,7 +148,7 @@
     <t>Calculate WV tax at 6.5% flat rate; WV income tax at 6.5% flat rate</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "WV tax calculated at 6.5% flat rate. Single-sales factor effective 2022+. Reference: WV Code 11-24-4, 11-24-7" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * wv_apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "WV tax calculated at 6.5% flat rate. Single-sales factor effective 2022+. Reference: WV Code 11-24-4, 11-24-7" to job.audit_trail;</t>
   </si>
   <si>
     <t>No WV nexus - no tax liability; No WV nexus - no tax</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>wv_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -236,36 +236,6 @@
   </si>
   <si>
     <t>WV economic nexus gross receipts threshold: $100,000</t>
-  </si>
-  <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>WV additions: federal NOL, foreign taxes deducted, state income taxes, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>WV</t>
-  </si>
-  <si>
-    <t>West Virginia state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>WV tax credits: economic development, jobs creation, research &amp; development, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>WV subtractions: qualified opportunity zone income, foreign source income, etc.</t>
   </si>
   <si>
     <t>state_tax_rate</t>
@@ -2554,14 +2524,14 @@
       <c r="B7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>65</v>
+      <c r="C7" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -2570,7 +2540,7 @@
         <v>67</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -2585,170 +2555,6 @@
         <v>14</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
